--- a/src/assets/paintings/Pantings Description.xlsx
+++ b/src/assets/paintings/Pantings Description.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karim\Projects\jadandari-portfolio\src\assets\paintings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D528C872-0875-4D1A-8A3F-628BD63F0AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D54DE95-0A39-4943-B45A-28689B396F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -84,6 +84,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -109,10 +116,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,22 +432,22 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
+      <c r="B9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>4</v>
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -447,10 +455,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
